--- a/elearning.edureka/src/test/resources/TestData.xlsx
+++ b/elearning.edureka/src/test/resources/TestData.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAMYA\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01A85D6-6547-4B13-84E0-80F3BAA70A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{151EC286-3710-4993-82EE-60F9BADD1D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="16200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExactCourseTitles" sheetId="1" r:id="rId1"/>
@@ -37,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">CaseKeywords!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CategoryPairs!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">CourseCategories!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CourseCategories_AC!$A$1:$A$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CourseCategories_AC!$A$1:$A$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">CourseSearchKeywords!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">EmptyWhitespaceInputs!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExactCourseTitles!$A$1:$A$4</definedName>
@@ -51,11 +46,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">WhitespaceKeywords!$A$1:$A$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:J32"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>CourseTitle</t>
   </si>
@@ -169,9 +165,6 @@
   </si>
   <si>
     <t>Programming &amp; Frameworks</t>
-  </si>
-  <si>
-    <t>Project Management and Methodologies</t>
   </si>
   <si>
     <t>Databases</t>
@@ -325,10 +318,10 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -963,31 +956,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+    <row r="3" spans="1:1" customFormat="1">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" customFormat="1">
       <c r="A4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" customFormat="1">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-    </row>
+    <row r="6" spans="1:1" customFormat="1"/>
+    <row r="7" spans="1:1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1004,23 +989,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
@@ -1050,50 +1035,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18.75">
       <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1116,15 +1101,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -1132,50 +1117,50 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18.75">
       <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1311,12 +1296,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/elearning.edureka/src/test/resources/TestData.xlsx
+++ b/elearning.edureka/src/test/resources/TestData.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{151EC286-3710-4993-82EE-60F9BADD1D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="12900" windowHeight="11025" firstSheet="16" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="ExactCourseTitles" sheetId="1" r:id="rId1"/>
@@ -24,15 +23,15 @@
     <sheet name="CourseCategories" sheetId="12" r:id="rId14"/>
     <sheet name="CourseSearchKeywords" sheetId="13" r:id="rId15"/>
     <sheet name="RapidSearchKeywords" sheetId="14" r:id="rId16"/>
-    <sheet name="CourseCategories_AC" sheetId="15" r:id="rId17"/>
-    <sheet name="CategoryPairs" sheetId="16" r:id="rId18"/>
+    <sheet name="CategoryPairs" sheetId="16" r:id="rId17"/>
+    <sheet name="CourseCatagories_AC" sheetId="20" r:id="rId18"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">WhitespaceKeywords!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">AutocompleteKeywords!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">CaseKeywords!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CategoryPairs!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CategoryPairs!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">CourseCategories!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">CourseCategories_AC!$A$1:$A$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">CourseSearchKeywords!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">EmptyWhitespaceInputs!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExactCourseTitles!$A$1:$A$4</definedName>
@@ -43,15 +42,27 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">RapidSearchKeywords!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">SearchKeywords!$A$1:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">SpecialCharacterInputs!$A$1:$A$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">WhitespaceKeywords!$A$1:$A$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <oleSize ref="A1:J32"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
   <si>
     <t>CourseTitle</t>
   </si>
@@ -65,6 +76,84 @@
     <t>DevOps</t>
   </si>
   <si>
+    <t>home url</t>
+  </si>
+  <si>
+    <t>https://www.edureka.co/</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>ramyajavalageri10@gmail.com</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Ramya@2004</t>
+  </si>
+  <si>
+    <t>password type</t>
+  </si>
+  <si>
+    <t>all course url</t>
+  </si>
+  <si>
+    <t>https://www.edureka.co/all-courses</t>
+  </si>
+  <si>
+    <t>all course contains</t>
+  </si>
+  <si>
+    <t>all-courses</t>
+  </si>
+  <si>
+    <t>AI url</t>
+  </si>
+  <si>
+    <t>https://www.edureka.co/artificial-intelligence-certification-courses</t>
+  </si>
+  <si>
+    <t>category name</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>AI url contains</t>
+  </si>
+  <si>
+    <t>artificial-intelligence-certification-courses</t>
+  </si>
+  <si>
+    <t>all courses url</t>
+  </si>
+  <si>
+    <t>all courses url contains</t>
+  </si>
+  <si>
+    <t>/all-courses</t>
+  </si>
+  <si>
+    <t>url contains</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>inavlid  ai url</t>
+  </si>
+  <si>
+    <t>https://www.edureka.co/invalid-ai-category-page</t>
+  </si>
+  <si>
+    <t>invalid AI url contais</t>
+  </si>
+  <si>
+    <t>invalid-ai-category-page</t>
+  </si>
+  <si>
     <t>Keyword</t>
   </si>
   <si>
@@ -89,6 +178,12 @@
     <t>data science</t>
   </si>
   <si>
+    <t>qzxv-98765</t>
+  </si>
+  <si>
+    <t>invalid-12345</t>
+  </si>
+  <si>
     <t>Input</t>
   </si>
   <si>
@@ -140,9 +235,6 @@
     <t>SearchKeyword</t>
   </si>
   <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
     <t>artifi</t>
   </si>
   <si>
@@ -164,116 +256,35 @@
     <t>artificial intelligence</t>
   </si>
   <si>
+    <t>Category1</t>
+  </si>
+  <si>
+    <t>Category2</t>
+  </si>
+  <si>
+    <t>Databases</t>
+  </si>
+  <si>
     <t>Programming &amp; Frameworks</t>
-  </si>
-  <si>
-    <t>Databases</t>
-  </si>
-  <si>
-    <t>Category1</t>
-  </si>
-  <si>
-    <t>Category2</t>
-  </si>
-  <si>
-    <t>home url</t>
-  </si>
-  <si>
-    <t>https://www.edureka.co/</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>ramyajavalageri10@gmail.com</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>Ramya@2004</t>
-  </si>
-  <si>
-    <t>password type</t>
-  </si>
-  <si>
-    <t>all course url</t>
-  </si>
-  <si>
-    <t>https://www.edureka.co/all-courses</t>
-  </si>
-  <si>
-    <t>all course contains</t>
-  </si>
-  <si>
-    <t>all-courses</t>
-  </si>
-  <si>
-    <t>AI url</t>
-  </si>
-  <si>
-    <t>https://www.edureka.co/artificial-intelligence-certification-courses</t>
-  </si>
-  <si>
-    <t>category name</t>
-  </si>
-  <si>
-    <t>AI url contains</t>
-  </si>
-  <si>
-    <t>artificial-intelligence-certification-courses</t>
-  </si>
-  <si>
-    <t>all courses url</t>
-  </si>
-  <si>
-    <t>all courses url contains</t>
-  </si>
-  <si>
-    <t>/all-courses</t>
-  </si>
-  <si>
-    <t>url contains</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>inavlid  ai url</t>
-  </si>
-  <si>
-    <t>https://www.edureka.co/invalid-ai-category-page</t>
-  </si>
-  <si>
-    <t>invalid AI url contais</t>
-  </si>
-  <si>
-    <t>invalid-ai-category-page</t>
-  </si>
-  <si>
-    <t>invalid-12345</t>
-  </si>
-  <si>
-    <t>qzxv-98765</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -283,9 +294,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color indexed="20"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -295,16 +305,360 @@
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -312,11 +666,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -324,17 +920,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -619,14 +1259,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
@@ -653,43 +1293,47 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -709,23 +1353,25 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -733,55 +1379,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -789,7 +1437,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -797,7 +1445,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -805,18 +1453,20 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -824,52 +1474,54 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -889,99 +1541,63 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" customFormat="1">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" customFormat="1">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" customFormat="1">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" customFormat="1"/>
-    <row r="7" spans="1:1" customFormat="1"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -989,215 +1605,253 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD403121-9395-490D-9A18-6F8258EC9849}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="44.5703125" customWidth="1"/>
+    <col min="1" max="1" width="23.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="44.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="ramyajavalageri10@gmail.com"/>
+    <hyperlink ref="B3" r:id="rId2" display="Ramya@2004"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="52.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
+      <c r="A2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>46</v>
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75">
-      <c r="A6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="mailto:ramyajavalageri10@gmail.com" xr:uid="{208E3CD7-7A18-4605-A3C9-69B929003D80}"/>
-    <hyperlink ref="B3" r:id="rId2" display="mailto:Ramya@2004" xr:uid="{EE7E39B0-F22C-412C-91D7-84AB18CAE48E}"/>
+    <hyperlink ref="B1" r:id="rId1" display="https://www.edureka.co/artificial-intelligence-certification-courses"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://www.edureka.co/all-courses"/>
+    <hyperlink ref="B7" r:id="rId3" display="https://www.edureka.co/invalid-ai-category-page"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D392AAC3-8D38-40DA-B98F-719BAC3D5204}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="52.5703125" customWidth="1"/>
-    <col min="2" max="2" width="62" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75">
-      <c r="A6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" xr:uid="{E40BE0B1-C850-45DD-A2D3-214A387DDBBF}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{D92E22BB-60C8-45D0-A7F6-8899EFA4AF3D}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{BF284405-1C10-44F5-BD61-CDC53EA7B5DD}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1207,23 +1861,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1231,7 +1887,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1239,30 +1895,32 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1276,96 +1934,105 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A4" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>